--- a/reports/member_funnel/downloads/member_funnel_7d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_target_segments.xlsx
@@ -492,16 +492,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -530,16 +522,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -568,16 +552,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -601,21 +577,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -644,16 +608,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -682,16 +638,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -720,16 +668,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -758,16 +698,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -796,16 +728,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -834,16 +758,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -867,21 +783,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -910,16 +814,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -948,16 +844,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -986,16 +874,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1024,16 +904,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1062,16 +934,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1100,16 +964,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1138,16 +994,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1176,16 +1024,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1209,21 +1049,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1247,21 +1075,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1285,21 +1101,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1323,21 +1127,9 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1352,7 +1144,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1361,21 +1153,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1390,7 +1170,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4829979824</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1399,21 +1179,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1428,7 +1196,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1437,21 +1205,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1466,7 +1222,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1475,21 +1231,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1504,7 +1248,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4829348219</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1513,21 +1257,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1542,7 +1274,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1551,21 +1283,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1580,7 +1300,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1589,21 +1309,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1627,21 +1335,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1670,16 +1366,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1708,16 +1396,8 @@
           <t>KAKAO_alimtalk</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1746,16 +1426,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1784,16 +1456,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1822,16 +1486,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1860,16 +1516,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1898,16 +1546,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1922,7 +1562,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1936,19 +1576,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1592,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4829440714</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1974,19 +1606,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2012,16 +1636,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2050,16 +1666,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2088,16 +1696,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2126,16 +1726,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2164,16 +1756,8 @@
           <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2202,16 +1786,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2240,16 +1816,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2264,13 +1832,13 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2278,19 +1846,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2302,13 +1862,13 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2316,19 +1876,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2340,13 +1892,13 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2354,19 +1906,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2392,16 +1936,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2430,16 +1966,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2454,7 +1982,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832076715</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -2463,24 +1991,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2501,21 +2017,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2530,7 +2034,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4830821550</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -2539,21 +2043,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2568,7 +2060,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -2577,24 +2069,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2615,21 +2095,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2644,7 +2112,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -2653,24 +2121,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2138,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>kk_4830821550</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -2691,21 +2147,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2720,7 +2164,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>kk_4832076715</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -2729,21 +2173,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2758,7 +2190,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -2767,24 +2199,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2805,21 +2225,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2834,13 +2242,13 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>kk_4832164589</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2848,19 +2256,11 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2872,13 +2272,13 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4832164589</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2886,19 +2286,11 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2302,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -2924,19 +2316,11 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2332,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -2962,16 +2346,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2986,7 +2362,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -3000,19 +2376,11 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3038,16 +2406,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -3076,16 +2436,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -3114,16 +2466,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -3138,7 +2482,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>saty31</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -3152,16 +2496,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3176,7 +2512,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -3190,16 +2526,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3214,7 +2542,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>kk_4832202047</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -3228,16 +2556,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3266,16 +2586,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3290,7 +2602,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kk_4832202047</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -3304,16 +2616,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3328,7 +2632,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>saty31</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -3342,16 +2646,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3380,16 +2676,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -3404,7 +2692,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kk_4832125929</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -3418,16 +2706,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3442,7 +2722,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -3456,16 +2736,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3480,7 +2752,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -3494,16 +2766,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3532,16 +2796,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3556,7 +2812,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -3570,16 +2826,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3594,7 +2842,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4832125929</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -3608,16 +2856,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3646,16 +2886,8 @@
           <t>KAKAO_alimtalk</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3684,16 +2916,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3722,16 +2946,8 @@
           <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3746,7 +2962,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>kk_4830963661</t>
+          <t>kk_4830923952</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -3760,19 +2976,11 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3784,7 +2992,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>kk_4830923952</t>
+          <t>kk_4830963661</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -3798,19 +3006,11 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3022,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -3836,16 +3036,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -3860,7 +3052,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -3874,19 +3066,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3082,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -3912,19 +3096,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3950,16 +3126,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3974,7 +3142,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -3988,16 +3156,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -4012,7 +3172,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -4026,19 +3186,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4050,7 +3202,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -4064,19 +3216,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4088,7 +3232,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -4102,19 +3246,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4126,7 +3262,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -4140,16 +3276,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -4164,7 +3292,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -4178,19 +3306,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4202,7 +3322,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -4216,19 +3336,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4240,7 +3352,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -4254,16 +3366,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -4278,7 +3382,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831468314</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -4292,16 +3396,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -4316,7 +3412,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -4330,19 +3426,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4354,7 +3442,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -4368,19 +3456,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4392,7 +3472,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -4406,19 +3486,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4430,7 +3502,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -4444,16 +3516,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -4482,16 +3546,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -4506,7 +3562,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -4520,19 +3576,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4558,16 +3606,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -4582,7 +3622,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -4596,16 +3636,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -4620,7 +3652,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -4634,16 +3666,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -4658,7 +3682,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -4672,19 +3696,11 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4696,7 +3712,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -4710,19 +3726,11 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4748,16 +3756,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -4781,21 +3781,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -4824,16 +3812,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -4857,21 +3837,9 @@
           <t>Owned Channel</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -4900,16 +3868,8 @@
           <t>da</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -4924,7 +3884,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -4933,24 +3893,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4962,7 +3910,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -4971,24 +3919,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5014,16 +3950,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5052,16 +3980,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -5076,7 +3996,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>kk_4830552074</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -5090,19 +4010,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5114,7 +4026,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4830552074</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -5128,19 +4040,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5166,16 +4070,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -5204,16 +4100,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -5237,21 +4125,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5266,7 +4142,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>kk_4829899341</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -5275,21 +4151,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5304,7 +4168,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4829899341</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -5313,21 +4177,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5351,21 +4203,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5394,16 +4234,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5432,16 +4264,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5456,7 +4280,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>kk_4829755741</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -5470,19 +4294,11 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5508,16 +4324,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -5532,7 +4340,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4829755741</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -5546,19 +4354,11 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5570,7 +4370,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -5584,16 +4384,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5608,7 +4400,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -5622,16 +4414,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5646,7 +4430,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4829674741</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -5660,16 +4444,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5684,7 +4460,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>kk_4830646394</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -5698,16 +4474,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5722,7 +4490,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>kk_4829674741</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -5736,16 +4504,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5760,7 +4520,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4830646394</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -5774,16 +4534,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5798,7 +4550,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -5812,16 +4564,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5850,16 +4594,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -5874,7 +4610,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>kk_4829543360</t>
+          <t>kk_4830264628</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -5888,16 +4624,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5912,7 +4640,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>kk_4829543360</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -5926,16 +4654,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5950,7 +4670,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -5964,16 +4684,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5988,7 +4700,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>kk_4830264628</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -6002,16 +4714,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6040,16 +4744,8 @@
           <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -6078,16 +4774,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6102,7 +4790,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -6116,16 +4804,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6140,7 +4820,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>kk_4830637852</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -6154,16 +4834,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6178,7 +4850,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>kk_4830497611</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -6192,16 +4864,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6216,7 +4880,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>kk_4830497611</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -6230,16 +4894,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6254,7 +4910,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -6268,19 +4924,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -6292,7 +4940,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -6306,16 +4954,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6330,7 +4970,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4830637852</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -6344,19 +4984,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -6368,7 +5000,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4830659012</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -6382,16 +5014,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6406,7 +5030,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>kk_4830659012</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -6420,16 +5044,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6458,16 +5074,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6496,16 +5104,8 @@
           <t>da</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -6520,7 +5120,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_4830137292</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -6534,19 +5134,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -6558,7 +5150,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>kk_4830137292</t>
+          <t>kk_4830540435</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -6572,19 +5164,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -6610,16 +5194,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -6634,7 +5210,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -6648,19 +5224,11 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -6672,7 +5240,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4829761376</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -6686,19 +5254,11 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -6724,16 +5284,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6762,16 +5314,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -6800,16 +5344,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -6838,16 +5374,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -6871,21 +5399,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6914,16 +5430,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -6938,7 +5446,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>kk_4828853669</t>
+          <t>kk_4828870663</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -6952,19 +5460,11 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -6976,7 +5476,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>kk_4828870663</t>
+          <t>kk_4828853669</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -6990,19 +5490,11 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -7028,16 +5520,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7066,16 +5550,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7104,16 +5580,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7142,16 +5610,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7180,16 +5640,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7218,16 +5670,8 @@
           <t>Heritage</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -7256,16 +5700,8 @@
           <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7294,16 +5730,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7332,16 +5760,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7356,7 +5776,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>kk_4829107379</t>
+          <t>kk_4828876907</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -7370,16 +5790,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7394,7 +5806,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>kk_4829201314</t>
+          <t>kk_4829107379</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -7408,16 +5820,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7432,7 +5836,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>kk_4828876907</t>
+          <t>kk_4829201314</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -7446,16 +5850,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7470,7 +5866,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>kk_4828872529</t>
+          <t>kk_4828903098</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -7484,19 +5880,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7508,7 +5896,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>kk_4828903098</t>
+          <t>kk_4828872529</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -7522,19 +5910,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -7560,16 +5940,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7598,16 +5970,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7636,16 +6000,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7674,16 +6030,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7712,16 +6060,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7750,16 +6090,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7788,16 +6120,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7826,16 +6150,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7864,16 +6180,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7902,16 +6210,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7940,16 +6240,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7978,16 +6270,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8016,16 +6300,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8054,16 +6330,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8092,16 +6360,8 @@
           <t>KAKAO_alimtalk</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8130,16 +6390,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8168,16 +6420,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8206,16 +6450,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8244,16 +6480,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8282,16 +6510,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8320,16 +6540,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8358,16 +6570,8 @@
           <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8396,16 +6600,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8429,21 +6625,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8467,21 +6651,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8505,21 +6677,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8548,16 +6708,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8586,16 +6738,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8624,16 +6768,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8662,16 +6798,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8700,16 +6828,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8738,16 +6858,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8776,16 +6888,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8814,16 +6918,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8852,16 +6948,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8890,16 +6978,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8928,16 +7008,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8952,7 +7024,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -8966,16 +7038,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8990,7 +7054,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -9004,16 +7068,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9042,16 +7098,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9075,21 +7123,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9118,16 +7154,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9151,21 +7179,9 @@
           <t>Owned Channel</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9189,21 +7205,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9232,16 +7236,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9270,16 +7266,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9308,16 +7296,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9346,16 +7326,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9384,16 +7356,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9422,16 +7386,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9460,16 +7416,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9498,16 +7446,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9536,16 +7476,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9574,16 +7506,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9612,16 +7536,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9650,16 +7566,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9688,16 +7596,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9726,16 +7626,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9764,16 +7656,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9797,21 +7681,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -9840,16 +7712,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9878,16 +7742,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9916,16 +7772,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9954,16 +7802,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9992,16 +7832,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10030,16 +7862,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10063,21 +7887,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10106,16 +7918,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10144,16 +7948,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10182,16 +7978,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10220,16 +8008,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10258,16 +8038,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10296,16 +8068,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10334,16 +8098,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10367,21 +8123,9 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10410,16 +8154,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10448,16 +8184,8 @@
           <t>KAKAO_alimtalk</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10486,16 +8214,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10524,16 +8244,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10562,16 +8274,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10600,16 +8304,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10624,7 +8320,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -10638,19 +8334,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -10662,7 +8350,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4829440714</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -10676,19 +8364,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10714,16 +8394,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10752,16 +8424,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10790,16 +8454,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10828,16 +8484,8 @@
           <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10866,16 +8514,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10890,13 +8530,13 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -10904,19 +8544,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10928,13 +8560,13 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -10942,19 +8574,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -10980,16 +8604,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11013,21 +8629,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11051,21 +8655,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11089,21 +8681,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11127,21 +8707,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11170,16 +8738,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11208,16 +8768,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11246,16 +8798,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11284,16 +8828,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11322,16 +8858,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11360,16 +8888,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
       <c r="H288" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11398,16 +8918,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11436,16 +8948,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11460,7 +8964,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -11474,16 +8978,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11498,7 +8994,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -11512,19 +9008,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -11536,7 +9024,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -11550,16 +9038,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11574,7 +9054,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -11588,19 +9068,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -11612,7 +9084,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -11626,19 +9098,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -11650,7 +9114,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -11664,16 +9128,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11688,7 +9144,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -11702,16 +9158,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11726,7 +9174,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -11740,19 +9188,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -11764,7 +9204,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831468314</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -11778,16 +9218,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11802,7 +9234,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
@@ -11816,16 +9248,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11840,7 +9264,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -11854,19 +9278,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -11878,7 +9294,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -11892,16 +9308,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11930,16 +9338,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11954,7 +9354,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -11968,19 +9368,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -11992,7 +9384,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -12006,16 +9398,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12030,7 +9414,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -12044,16 +9428,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12068,7 +9444,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -12082,19 +9458,11 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -12106,7 +9474,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -12120,19 +9488,11 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -12153,21 +9513,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12196,16 +9544,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12229,21 +9569,9 @@
           <t>Owned Channel</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12272,16 +9600,8 @@
           <t>da</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12296,7 +9616,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -12305,24 +9625,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E313" t="inlineStr"/>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -12334,7 +9642,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -12343,24 +9651,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -12386,16 +9682,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12424,16 +9712,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12462,16 +9742,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12500,16 +9772,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12524,7 +9788,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>kk_4829255442</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -12538,16 +9802,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12562,7 +9818,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4829255442</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -12576,16 +9832,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12614,16 +9862,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12652,16 +9892,8 @@
           <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12690,16 +9922,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12728,16 +9952,8 @@
           <t>da</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12766,16 +9982,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12804,16 +10012,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12828,7 +10028,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -12842,19 +10042,11 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -12866,7 +10058,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4829761376</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
@@ -12880,19 +10072,11 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -12918,16 +10102,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12956,16 +10132,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12994,16 +10162,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -13032,16 +10192,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -13070,16 +10222,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -13108,16 +10252,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -13146,16 +10282,8 @@
           <t>Heritage</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -13184,16 +10312,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -13222,16 +10342,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr"/>
       <c r="H337" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -13260,16 +10372,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr">
         <is>
           <t>GENERAL</t>

--- a/reports/member_funnel/downloads/member_funnel_7d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_target_segments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H338"/>
+  <dimension ref="A1:H332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,25 +478,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kk_4831361074</t>
+          <t>kk_4830885654</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>kk_4830254905</t>
+          <t>kk_4831895164</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kk_4832204677</t>
+          <t>ydh1184</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -549,14 +549,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -568,21 +568,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kk_4830885654</t>
+          <t>kk_4832961884</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -594,25 +598,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kk_4831895164</t>
+          <t>kk_4832593419</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -624,18 +628,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -654,18 +658,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -684,18 +688,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>kk_4833676515</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -714,25 +718,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_4833576113</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -744,25 +748,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kk_4830030364</t>
+          <t>kk_4832799612</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -774,7 +778,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kk_4830247238</t>
+          <t>kk_4832659421</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -783,7 +787,11 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -800,18 +808,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kk_4830591832</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -890,7 +898,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kk_4832293158</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -908,7 +916,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -920,7 +928,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kk_4832162309</t>
+          <t>kk_4832293158</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -931,7 +939,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -950,18 +958,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>kk_4831572710</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -980,18 +988,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kda01126</t>
+          <t>kk_4833855255</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1010,18 +1018,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>masterk</t>
+          <t>kk_4832162309</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1040,21 +1048,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>kk_4832411690</t>
+          <t>kk_4833840470</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026​</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1078,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>kk_4832425261</t>
+          <t>kk_4830212469</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1092,21 +1108,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>kk_4832425669</t>
+          <t>kk_4833715500</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1138,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>masterk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -1127,7 +1147,11 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
@@ -1144,7 +1168,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>sjjeon1928</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1153,7 +1177,11 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
@@ -1170,7 +1198,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1179,12 +1207,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1228,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1205,12 +1237,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1258,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1231,12 +1267,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1288,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>whitehole147</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1257,7 +1297,11 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
@@ -1274,7 +1318,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4833013784</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1283,7 +1327,11 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
@@ -1300,7 +1348,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1309,12 +1357,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1378,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>kk_4829294214</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1335,12 +1387,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1352,25 +1408,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>kk_4829088785</t>
+          <t>arumabc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1382,25 +1438,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>rkddl4</t>
+          <t>kk_4832411690</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1412,18 +1468,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_4833617385</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -1442,25 +1498,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>kk_4831842028</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1472,18 +1528,18 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>kk_4830513865</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1502,25 +1558,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>kk_4829077261</t>
+          <t>kk_4832556634</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1532,25 +1588,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>kk_4830476438</t>
+          <t>kk_4833397488</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1562,25 +1618,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1592,25 +1648,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4833115356</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1678,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>kk_4830793813</t>
+          <t>dave1102</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1633,14 +1689,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1708,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>charismasm74</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1663,14 +1719,14 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1738,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>kk_4831500868</t>
+          <t>kk_4832562814</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1712,7 +1768,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kk_4830922114</t>
+          <t>kk_4833867742</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1723,14 +1779,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1798,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>hoonck1</t>
+          <t>kk_4832564458</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1753,14 +1809,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1772,25 +1828,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1802,18 +1858,18 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kk_4831768959</t>
+          <t>kk_4832735078</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -1832,25 +1888,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4832986577</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1862,18 +1918,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>wngml5609</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -1892,25 +1948,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4832771015</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1978,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kk_4832105165</t>
+          <t>ckddbs4958</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1933,7 +1989,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -1952,25 +2008,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kk_4831842112</t>
+          <t>kk_4833234218</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1982,21 +2038,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kk_4832076715</t>
+          <t>kk_4833435690</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2008,16 +2068,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>kk_4832114535</t>
+          <t>kk_4833215714</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
@@ -2034,16 +2098,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>kk_4830821550</t>
+          <t>kk_4832874454</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
@@ -2060,21 +2128,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4833692238</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>[PF]전환_회원가입(유사)</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2086,21 +2158,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4833915167</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>[PF]트래픽_유사+관심사</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2112,21 +2188,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2138,21 +2218,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2164,21 +2248,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2190,21 +2278,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4833937502</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2216,16 +2308,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>kk_4832963009</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
@@ -2242,18 +2338,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2272,18 +2368,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>kk_4832164589</t>
+          <t>kk_4833788564</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -2302,18 +2398,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>hlpt10</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2332,25 +2428,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4832855902</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2362,18 +2458,18 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4832804456</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2392,25 +2488,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2422,18 +2518,18 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -2452,25 +2548,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4832527479</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2578,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -2493,14 +2589,14 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2608,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>jinchoi24</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -2523,7 +2619,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -2542,7 +2638,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>kk_4832202047</t>
+          <t>kk_4832811973</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -2553,7 +2649,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -2572,7 +2668,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>kk_4832151833</t>
+          <t>kk_4833676329</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -2583,14 +2679,14 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2698,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>kk_4833836842</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -2613,14 +2709,14 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2632,18 +2728,18 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>saty31</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -2662,25 +2758,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>kk_4832154317</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2692,18 +2788,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -2722,18 +2818,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4833961109</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -2752,18 +2848,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4833294708</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -2782,18 +2878,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>kk_4831536902</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -2812,18 +2908,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4833706874</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -2842,18 +2938,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>kk_4832125929</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -2872,18 +2968,18 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>kk_4830943389</t>
+          <t>kk_4833232918</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -2902,18 +2998,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>kk_4831612250</t>
+          <t>pjj1758</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -2932,25 +3028,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>kk_4830988405</t>
+          <t>rkddl4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2962,25 +3058,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>kk_4830923952</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2992,25 +3088,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>kk_4830963661</t>
+          <t>kk_4831842028</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3022,25 +3118,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4830513865</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3052,25 +3148,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4830476438</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3178,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -3100,7 +3196,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3112,25 +3208,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>kk_4832100101</t>
+          <t>kk_4830793813</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3142,25 +3238,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3172,25 +3268,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831500868</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3202,25 +3298,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4830922114</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3232,13 +3328,13 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3262,7 +3358,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -3292,7 +3388,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831768959</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -3322,13 +3418,13 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3352,7 +3448,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -3382,25 +3478,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832105165</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3508,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4831842112</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -3430,7 +3526,7 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3442,25 +3538,25 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3472,18 +3568,18 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -3502,18 +3598,18 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -3532,25 +3628,25 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3562,25 +3658,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3592,25 +3688,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>kk_4831723596</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3622,25 +3718,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>kk_4830821550</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3652,25 +3748,25 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4832114535</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3682,25 +3778,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4832076715</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3712,25 +3808,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3838,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>kk_4828653802</t>
+          <t>kk_4832164589</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -3772,16 +3868,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>kk_4829795736</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
@@ -3798,18 +3898,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>kk_3964942719</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -3828,16 +3928,20 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>kk_4828995903</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
@@ -3854,25 +3958,25 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3884,21 +3988,25 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3910,16 +4018,20 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
@@ -3936,25 +4048,25 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>kk_4830462005</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3966,7 +4078,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>kk_4829888934</t>
+          <t>kk_4832151833</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -3977,14 +4089,14 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3996,25 +4108,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4832202047</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4026,18 +4138,18 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>kk_4830552074</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -4056,25 +4168,25 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>kk_4829567584</t>
+          <t>saty31</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4198,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>kk_4829654698</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4097,14 +4209,14 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4116,16 +4228,20 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>kk_4829843383</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
@@ -4142,21 +4258,25 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4832154317</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>EFW</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4168,16 +4288,20 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>kk_4829899341</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
@@ -4194,16 +4318,20 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>kk_4830179868</t>
+          <t>kk_4832125929</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
@@ -4220,18 +4348,18 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>kk_4829500046</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -4250,18 +4378,18 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>kk_4830568801</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -4280,25 +4408,25 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4310,25 +4438,25 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>kk_4829255442</t>
+          <t>kk_4830943389</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4340,18 +4468,18 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>kk_4829755741</t>
+          <t>kk_4831612250</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -4370,7 +4498,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4830988405</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -4381,7 +4509,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -4400,25 +4528,25 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4430,25 +4558,25 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>kk_4829674741</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4460,18 +4588,18 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4832100101</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -4490,18 +4618,18 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -4520,25 +4648,25 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>kk_4830646394</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4550,25 +4678,25 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4580,25 +4708,25 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>akita1129</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4610,25 +4738,25 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>kk_4830264628</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4640,25 +4768,25 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>kk_4829543360</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4670,18 +4798,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -4700,25 +4828,25 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4730,18 +4858,18 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>kk_4830253885</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -4760,7 +4888,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>kk_4829512827</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -4771,14 +4899,14 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4790,25 +4918,25 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4820,25 +4948,25 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4850,18 +4978,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>kk_4831723596</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -4880,18 +5008,18 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>kk_4830497611</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -4910,18 +5038,18 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -4940,25 +5068,25 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4970,25 +5098,25 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>kk_4830637852</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5000,25 +5128,25 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>kk_4830659012</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5030,25 +5158,25 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5060,25 +5188,25 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>kk_4830760298</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5218,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>kk_4830212469</t>
+          <t>kk_3964942719</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -5101,14 +5229,14 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5120,25 +5248,25 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>kk_4830137292</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5150,25 +5278,25 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5308,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>susaeg202</t>
+          <t>kk_4830462005</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -5191,14 +5319,14 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5210,25 +5338,25 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4830552074</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5240,25 +5368,25 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5270,18 +5398,18 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>kk_4828679899</t>
+          <t>kk_4830179868</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -5300,25 +5428,25 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>kk_4828662042</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5330,25 +5458,25 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>kk_4828953106</t>
+          <t>kk_4830568801</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5360,18 +5488,18 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -5390,16 +5518,20 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>kk_4829004394</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
@@ -5416,25 +5548,25 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>kk_4829016429</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5578,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>kk_4828870663</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -5457,14 +5589,14 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5608,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>kk_4828853669</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -5487,7 +5619,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -5506,18 +5638,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>kk_4829012080</t>
+          <t>kk_4830646394</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -5536,7 +5668,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>gee04171</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -5566,18 +5698,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>kk_4829143684</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -5596,18 +5728,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>kk_4828900771</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -5626,25 +5758,25 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>kk_4828729325</t>
+          <t>kk_4830264628</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5656,18 +5788,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>kk_4828995176</t>
+          <t>kk_4830253885</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Heritage</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -5686,18 +5818,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>kk_4828781963</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -5716,18 +5848,18 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>kk_4829073557</t>
+          <t>kk_4830497611</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -5746,7 +5878,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>kk_4828671248</t>
+          <t>kk_4830637852</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -5776,7 +5908,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>kk_4828876907</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -5806,7 +5938,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>kk_4829107379</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -5824,7 +5956,7 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5968,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>kk_4829201314</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -5866,25 +5998,25 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>kk_4828903098</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5896,18 +6028,18 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>kk_4828872529</t>
+          <t>kk_4830659012</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -5926,25 +6058,25 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>kk_4828987324</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5956,18 +6088,18 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>kk_4828986759</t>
+          <t>kk_4830760298</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -5981,42 +6113,42 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>kk_4831361074</t>
+          <t>kk_4830137292</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>kk_4830254905</t>
+          <t>kk_4830540435</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -6041,12 +6173,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>kk_4832204677</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -6057,7 +6189,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -6082,7 +6214,7 @@
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6106,18 +6238,18 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -6136,18 +6268,18 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -6166,18 +6298,18 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>kk_4833676515</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -6196,7 +6328,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_4832269209</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -6226,18 +6358,18 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>kk_4830030364</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -6256,7 +6388,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>kk_4832269209</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -6286,18 +6418,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>kk_4831572710</t>
+          <t>kk_4833855255</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -6316,18 +6448,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>kda01126</t>
+          <t>kk_4833840470</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -6346,18 +6478,18 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>rkddl4</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -6376,18 +6508,18 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>kk_4830513865</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -6406,18 +6538,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>kk_4829077261</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -6436,7 +6568,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>kk_4830476438</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -6447,7 +6579,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -6466,18 +6598,18 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -6496,18 +6628,18 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>charismasm74</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -6526,18 +6658,18 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>kk_4830922114</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -6556,7 +6688,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>hoonck1</t>
+          <t>kk_4832804456</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -6567,7 +6699,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -6586,18 +6718,18 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -6616,16 +6748,20 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr">
@@ -6642,16 +6778,20 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4833676329</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
@@ -6668,16 +6808,20 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>rkddl4</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr"/>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
@@ -6694,18 +6838,18 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4830513865</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -6724,7 +6868,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4830476438</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -6735,7 +6879,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -6754,18 +6898,18 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -6784,18 +6928,18 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -6814,18 +6958,18 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4830922114</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -6844,18 +6988,18 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -6874,18 +7018,18 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>kk_4832154317</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -6904,18 +7048,18 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -6934,18 +7078,18 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -6964,18 +7108,18 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -6994,18 +7138,18 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -7024,18 +7168,18 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -7054,18 +7198,18 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -7084,18 +7228,18 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -7114,16 +7258,20 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>kk_4829795736</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
@@ -7140,7 +7288,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>kk_3964942719</t>
+          <t>kk_4832154317</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -7151,7 +7299,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -7170,16 +7318,20 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>kk_4828995903</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
@@ -7196,16 +7348,20 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr">
@@ -7222,7 +7378,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>kk_4829888934</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -7233,7 +7389,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -7252,18 +7408,18 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -7282,7 +7438,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>kk_4829654698</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -7293,7 +7449,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -7312,7 +7468,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>akita1129</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -7323,7 +7479,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -7342,18 +7498,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -7372,7 +7528,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_3964942719</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -7383,7 +7539,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -7402,18 +7558,18 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>susaeg202</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -7432,18 +7588,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -7462,13 +7618,13 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>kk_4828953106</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -7492,18 +7648,18 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>kk_4829016429</t>
+          <t>kk_4830540435</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -7522,7 +7678,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>kk_4828729325</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -7533,7 +7689,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -7547,30 +7703,30 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>high_intent</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>kk_4828987324</t>
+          <t>kk_4830885654</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7582,18 +7738,18 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>kk_4831361074</t>
+          <t>kk_4831895164</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -7612,7 +7768,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>kk_4830254905</t>
+          <t>kk_4832593419</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -7623,14 +7779,14 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7642,18 +7798,18 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>kk_4832204677</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -7672,21 +7828,25 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>kk_4830885654</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -7698,18 +7858,18 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>kk_4831895164</t>
+          <t>kk_4833676515</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -7728,25 +7888,25 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_4832659421</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7758,25 +7918,25 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7788,13 +7948,13 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>kk_4832269209</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -7818,7 +7978,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -7848,25 +8008,25 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>kk_4830030364</t>
+          <t>kk_4832293158</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7878,21 +8038,25 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>kk_4830247238</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -7904,25 +8068,25 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>kk_4830591832</t>
+          <t>kk_4833855255</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -7934,7 +8098,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>kk_4832269209</t>
+          <t>kk_4832162309</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -7945,14 +8109,14 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7964,7 +8128,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>kk_4832293158</t>
+          <t>kk_4833840470</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -7975,14 +8139,14 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -7994,18 +8158,18 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>kk_4832162309</t>
+          <t>kk_4830212469</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>da</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -8024,7 +8188,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>kk_4831572710</t>
+          <t>kk_4833715500</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -8035,14 +8199,14 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8218,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>kda01126</t>
+          <t>masterk</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -8065,14 +8229,14 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8084,25 +8248,25 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>masterk</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8114,21 +8278,25 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr"/>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8140,18 +8308,18 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>kk_4829088785</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -8170,18 +8338,18 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>rkddl4</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -8200,18 +8368,18 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>kk_4831842028</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -8230,18 +8398,18 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>kk_4830513865</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -8260,18 +8428,18 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>kk_4829077261</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -8290,25 +8458,25 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>kk_4830476438</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8320,25 +8488,25 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8350,18 +8518,18 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4833435690</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -8380,7 +8548,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>kk_4830793813</t>
+          <t>kk_4833692238</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -8391,7 +8559,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -8410,18 +8578,18 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>charismasm74</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -8440,25 +8608,25 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>kk_4830922114</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8470,25 +8638,25 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>hoonck1</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8668,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4832963009</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -8530,13 +8698,13 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -8548,7 +8716,7 @@
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8560,25 +8728,25 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4832855902</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8758,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>kk_4831842112</t>
+          <t>kk_4832804456</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -8608,7 +8776,7 @@
       <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8620,21 +8788,25 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
       <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8646,16 +8818,20 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
@@ -8672,16 +8848,20 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
@@ -8698,21 +8878,25 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>kk_4833676329</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8724,25 +8908,25 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4833836842</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8754,18 +8938,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>rkddl4</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -8784,25 +8968,25 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4831842028</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8814,18 +8998,18 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4830513865</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -8844,7 +9028,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4830476438</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -8855,7 +9039,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -8874,18 +9058,18 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -8904,7 +9088,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>kk_4832154317</t>
+          <t>kk_4830793813</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -8915,14 +9099,14 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8934,7 +9118,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>kk_4830923952</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -8945,14 +9129,14 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8964,25 +9148,25 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4830922114</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8994,13 +9178,13 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9024,7 +9208,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -9054,13 +9238,13 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9084,18 +9268,18 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4831842112</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -9114,25 +9298,25 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9144,25 +9328,25 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9174,18 +9358,18 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -9204,18 +9388,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -9234,25 +9418,25 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9264,18 +9448,18 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -9294,18 +9478,18 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -9324,25 +9508,25 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9354,25 +9538,25 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9384,18 +9568,18 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -9414,7 +9598,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4832154317</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -9425,7 +9609,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -9444,25 +9628,25 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9474,18 +9658,18 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -9504,21 +9688,25 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>kk_4829795736</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9530,18 +9718,18 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>kk_3964942719</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -9560,21 +9748,25 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>kk_4828995903</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9586,18 +9778,18 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -9616,21 +9808,25 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9642,21 +9838,25 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9668,7 +9868,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>kk_4829888934</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -9679,14 +9879,14 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9698,18 +9898,18 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -9728,13 +9928,13 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>kk_4829567584</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -9758,7 +9958,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>kk_4829654698</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -9769,7 +9969,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
@@ -9788,18 +9988,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -9818,25 +10018,25 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>kk_4829255442</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9848,7 +10048,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>akita1129</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -9859,7 +10059,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -9878,18 +10078,18 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>kk_4830253885</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F322" t="inlineStr"/>
@@ -9908,18 +10108,18 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -9938,7 +10138,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>kk_4830212469</t>
+          <t>kk_3964942719</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -9949,14 +10149,14 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9968,18 +10168,18 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
@@ -9998,25 +10198,25 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>susaeg202</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10028,18 +10228,18 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
@@ -10058,18 +10258,18 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -10088,18 +10288,18 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>kk_4828662042</t>
+          <t>kk_4830253885</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
@@ -10118,13 +10318,13 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>kk_4828953106</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10148,7 +10348,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>kk_4830540435</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
@@ -10166,7 +10366,7 @@
       <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -10178,18 +10378,18 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>kk_4829016429</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F332" t="inlineStr"/>
@@ -10197,186 +10397,6 @@
       <c r="H332" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>high_intent</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>kk_4828870663</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>(organic)</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr"/>
-      <c r="G333" t="inlineStr"/>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>HIGH_INTENT_NUDGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>high_intent</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>kk_4828729325</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>EFW</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr"/>
-      <c r="G334" t="inlineStr"/>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>high_intent</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>kk_4828995176</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>Official SNS</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>Heritage</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr"/>
-      <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>HIGH_INTENT_NUDGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>high_intent</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>kk_4828903098</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>HIGH_INTENT_NUDGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>high_intent</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>kk_4828987324</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr"/>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>naversa_mo</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr"/>
-      <c r="G337" t="inlineStr"/>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>repeat_buyer</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>kk_4828788256</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr"/>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr"/>
-      <c r="G338" t="inlineStr"/>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_7d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_target_segments.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kk_4833894015</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>kk_4832656308</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>kk_4832738942</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>kk_4833682381</t>
+          <t>arumabc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1276,7 +1276,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>whitehole147</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1306,7 +1306,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>kk_4833013784</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1336,7 +1336,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kk_4833797203</t>
+          <t>kk_4833013784</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1366,7 +1366,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>kk_4832648970</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1396,7 +1396,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>arumabc</t>
+          <t>whitehole147</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kk_4833617385</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4833617385</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1546,7 +1546,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>kk_4833397488</t>
+          <t>kk_4832564458</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kk_4833698569</t>
+          <t>kk_4833397488</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>kk_4833115356</t>
+          <t>kk_4833867742</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>ckddbs4958</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1726,7 +1726,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>kk_4832562814</t>
+          <t>kk_4833115356</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kk_4833867742</t>
+          <t>kk_4832735078</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kk_4832564458</t>
+          <t>kk_4832986577</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kk_4832425261</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kk_4832735078</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1876,7 +1876,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>kk_4832986577</t>
+          <t>wngml5609</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>wngml5609</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ckddbs4958</t>
+          <t>kk_4832562814</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kk_4833234218</t>
+          <t>kk_4832874454</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>kk_4832874454</t>
+          <t>kk_4833234218</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>kk_4833289287</t>
+          <t>kk_4833937502</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -2206,7 +2206,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -2236,7 +2236,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>kk_4833858368</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -2266,7 +2266,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>kk_4833937502</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>kk_4832497383</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -2356,7 +2356,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>hlpt10</t>
+          <t>kk_4832855902</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -2416,7 +2416,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kk_4832855902</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>kk_4832888908</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -2506,7 +2506,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>mystyle1999</t>
+          <t>hlpt10</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>kk_4832527479</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -2566,7 +2566,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>kk_4832745335</t>
+          <t>kk_4832527479</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -2596,7 +2596,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4833294708</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4833232918</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>kk_4833961109</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>kk_4833294708</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>pjj1758</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>kk_4833706874</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>kk_4833232918</t>
+          <t>kk_4833706874</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>pjj1758</t>
+          <t>kk_4833961109</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_4831842028</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>kk_4831842028</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -3106,7 +3106,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4831768959</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -3376,7 +3376,7 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>kk_4831768959</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -3466,7 +3466,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>kk_4832105165</t>
+          <t>kk_4831842112</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>kk_4831842112</t>
+          <t>kk_4832105165</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -3526,7 +3526,7 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -3586,7 +3586,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -3616,7 +3616,7 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -3706,7 +3706,7 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>kk_4832114535</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4832114535</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -3946,7 +3946,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -4006,7 +4006,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>kk_4832100101</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -4606,7 +4606,7 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -4636,7 +4636,7 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -4696,7 +4696,7 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -4816,7 +4816,7 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4832100101</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -4846,7 +4846,7 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -4876,7 +4876,7 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -4906,7 +4906,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -4936,7 +4936,7 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -4966,7 +4966,7 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -5026,7 +5026,7 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -5056,7 +5056,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -5176,7 +5176,7 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -5206,7 +5206,7 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -5296,7 +5296,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>kk_4830179868</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4830179868</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -5836,7 +5836,7 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -5956,7 +5956,7 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>kk_4833894015</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>kk_4833733292</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>kk_4833894015</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>kk_4832656308</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -8266,7 +8266,7 @@
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>kk_4832738942</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>kk_4833797203</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>kk_4832648970</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -8386,7 +8386,7 @@
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>kk_4833733292</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -8428,7 +8428,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -8626,7 +8626,7 @@
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>kk_4832497383</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -8716,7 +8716,7 @@
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8758,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>kk_4832804456</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -8776,7 +8776,7 @@
       <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>kk_4832888908</t>
+          <t>kk_4832804456</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -8806,7 +8806,7 @@
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9208,13 +9208,13 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9226,7 +9226,7 @@
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9238,13 +9238,13 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9256,7 +9256,7 @@
       <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -9316,7 +9316,7 @@
       <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -9406,7 +9406,7 @@
       <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -9628,7 +9628,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -9676,7 +9676,7 @@
       <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -9706,7 +9706,7 @@
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -9736,7 +9736,7 @@
       <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -9826,7 +9826,7 @@
       <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -9886,7 +9886,7 @@
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -9916,7 +9916,7 @@
       <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -9946,7 +9946,7 @@
       <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -9976,7 +9976,7 @@
       <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -10048,7 +10048,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -10096,7 +10096,7 @@
       <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -10126,7 +10126,7 @@
       <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -10186,7 +10186,7 @@
       <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
@@ -10216,7 +10216,7 @@
       <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
